--- a/demo-StatsPAI-skill/tables/table3_heterogeneity.xlsx
+++ b/demo-StatsPAI-skill/tables/table3_heterogeneity.xlsx
@@ -53,7 +53,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -62,7 +62,30 @@
       <diagonal/>
     </border>
     <border>
-      <bottom style="medium"/>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -70,17 +93,23 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -449,16 +478,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -469,224 +498,706 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>(1) All</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>(2) Black</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>(3) Non-black</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>(4) South</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>(5) Non-south</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>(6) SMSA</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>(7) Non-SMSA</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>(1) All</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>(2) Black</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>(3) Non-black</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>(4) South</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>(5) Non-south</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>(6) SMSA</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>(7) Non-SMSA</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>4.734***</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>2.476***</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>4.686***</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>231844238082004.656</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>4.762***</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>2.425***</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>4.867***</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>(0.070)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>(0.075)</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>(0.079)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>(4141688650879277203456.000)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>(0.089)</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>(0.043)</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>(0.126)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Years of schooling</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>0.074***</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>0.071***</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>0.074***</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>0.259</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>0.070***</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>0.075***</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>0.070***</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>(0.004)</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>(0.008)</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>(0.004)</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>()</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>(0.005)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>(0.004)</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>(0.007)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>exper</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>0.084***</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0.034**</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>0.090***</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>0.327</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>0.087***</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>0.089***</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>0.068***</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>(0.007)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>(0.014)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>(0.008)</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>(137363.606)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>(0.009)</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>(0.009)</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>(0.010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>expersq</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>-0.002***</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>-0.002***</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>-0.009</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-0.002***</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>-0.002***</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>-0.002***</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>(0.001)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>(8955.173)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>-0.190***</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>2.476***</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>-0.049</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>-0.123***</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>-0.175***</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>-0.231***</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>(0.017)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>(0.075)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>()</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>()</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>(0.029)</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>(0.021)</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>(0.034)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>south</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>-0.125***</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>-0.214***</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>-0.100***</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>-231844238082004.094</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>-0.125***</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>-0.114***</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>(0.015)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>(0.034)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>(0.017)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>(6047170633136027467776.000)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>(0.018)</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>(0.029)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>smsa</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>0.161***</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0.143***</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>0.155***</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>0.184***</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>0.153***</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>2.425***</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>(0.015)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>(0.033)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>(0.017)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>(0.032)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>(0.021)</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>(0.043)</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>3,010</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>703</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>2,307</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>1,215</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>1,795</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>2,146</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>864</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>R²</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>0.291</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>0.266</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>0.216</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>-0.609</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>-0.607</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>0.187</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>0.233</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>0.294</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Standard errors in parentheses</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>* p&lt;0.10, ** p&lt;0.05, *** p&lt;0.01</t>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>*** p&lt;0.01, ** p&lt;0.05, * p&lt;0.10</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>